--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Libuš/Databaze Libuš 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Libuš/Databaze Libuš 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4958" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5028" uniqueCount="391">
   <si>
     <t>Datum</t>
   </si>
@@ -465,6 +465,21 @@
     <t>19.05.2026</t>
   </si>
   <si>
+    <t>20.05.2026</t>
+  </si>
+  <si>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>14 min 23 s</t>
+  </si>
+  <si>
+    <t>21.05.2026</t>
+  </si>
+  <si>
+    <t>11 min 10 s</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
@@ -481,9 +496,6 @@
   </si>
   <si>
     <t>21:30</t>
-  </si>
-  <si>
-    <t>04:30</t>
   </si>
   <si>
     <t>10 min 59 s</t>
@@ -5521,6 +5533,438 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M114" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="N114" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O114" s="3">
+        <v>450.0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M115" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N115" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O115" s="3">
+        <v>225.0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M116" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N116" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O116" s="3">
+        <v>180.0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P117" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q117" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="R117" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S117" s="3">
+        <v>13572.1</v>
+      </c>
+      <c r="T117" s="3">
+        <v>6044.0</v>
+      </c>
+      <c r="U117" s="3">
+        <v>11005.0</v>
+      </c>
+      <c r="V117" s="3">
+        <v>8535.0</v>
+      </c>
+      <c r="W117" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X117" s="3">
+        <v>1520.0</v>
+      </c>
+      <c r="Y117" s="3">
+        <v>1374.0</v>
+      </c>
+      <c r="Z117" s="3">
+        <v>1100.0</v>
+      </c>
+      <c r="AA117" s="3">
+        <v>6487.0</v>
+      </c>
+      <c r="AB117" s="3">
+        <v>49022.1</v>
+      </c>
+      <c r="AC117" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD117" s="3">
+        <v>0.24094393692482743</v>
+      </c>
+      <c r="AH117" s="3">
+        <v>50.0</v>
+      </c>
+      <c r="AI117" s="3">
+        <v>855.0</v>
+      </c>
+      <c r="AJ117" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK117" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL117" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="AM117" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AN117" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AO117" s="3">
+        <v>103.0</v>
+      </c>
+      <c r="AP117" s="3">
+        <v>19.0</v>
+      </c>
+      <c r="AQ117" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR117" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS117" s="3">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="AT117" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU117" s="3">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="AV117" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L121" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M121" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="N121" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O121" s="3">
+        <v>945.0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M122" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="P123" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="Q123" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R123" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S123" s="3">
+        <v>10493.0</v>
+      </c>
+      <c r="T123" s="3">
+        <v>5445.0</v>
+      </c>
+      <c r="U123" s="3">
+        <v>9539.0</v>
+      </c>
+      <c r="V123" s="3">
+        <v>8421.0</v>
+      </c>
+      <c r="W123" s="3">
+        <v>329.0</v>
+      </c>
+      <c r="X123" s="3">
+        <v>650.0</v>
+      </c>
+      <c r="Y123" s="3">
+        <v>1651.0</v>
+      </c>
+      <c r="AA123" s="3">
+        <v>2342.0</v>
+      </c>
+      <c r="AB123" s="3">
+        <v>39665.0</v>
+      </c>
+      <c r="AC123" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD123" s="3">
+        <v>0.2725118994156708</v>
+      </c>
+      <c r="AE123" s="3">
+        <v>500.0</v>
+      </c>
+      <c r="AI123" s="3">
+        <v>945.0</v>
+      </c>
+      <c r="AJ123" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK123" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL123" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="AM123" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AN123" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO123" s="3">
+        <v>97.0</v>
+      </c>
+      <c r="AP123" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="AQ123" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="AR123" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS123" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="AT123" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU123" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="AV123" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5681,7 +6125,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>103</v>
@@ -5701,7 +6145,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>103</v>
@@ -5730,7 +6174,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>103</v>
@@ -5784,7 +6228,7 @@
         <v>1.0</v>
       </c>
       <c r="AM4" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="AN4" s="3">
         <v>1.0</v>
@@ -5816,7 +6260,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>108</v>
@@ -5836,7 +6280,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>108</v>
@@ -5856,7 +6300,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>108</v>
@@ -5876,7 +6320,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>108</v>
@@ -5896,7 +6340,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>108</v>
@@ -5929,7 +6373,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>108</v>
@@ -5990,7 +6434,7 @@
         <v>6.0</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AN10" s="3">
         <v>1.0</v>
@@ -6022,7 +6466,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -6042,7 +6486,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -6054,15 +6498,15 @@
         <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
@@ -6082,7 +6526,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -6111,7 +6555,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -6134,7 +6578,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>49</v>
@@ -6197,7 +6641,7 @@
         <v>0.0</v>
       </c>
       <c r="AM16" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AN16" s="3">
         <v>1.0</v>
@@ -6229,7 +6673,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>68</v>
@@ -6249,7 +6693,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>68</v>
@@ -6269,7 +6713,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>68</v>
@@ -6289,7 +6733,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>68</v>
@@ -6309,7 +6753,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>68</v>
@@ -6338,7 +6782,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>68</v>
@@ -6367,7 +6811,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>68</v>
@@ -6430,7 +6874,7 @@
         <v>1.0</v>
       </c>
       <c r="AM23" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="AN23" s="3">
         <v>2.0</v>
@@ -6462,7 +6906,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>76</v>
@@ -6482,7 +6926,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>76</v>
@@ -6502,7 +6946,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>76</v>
@@ -6531,7 +6975,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>76</v>
@@ -6560,7 +7004,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>76</v>
@@ -6620,7 +7064,7 @@
         <v>0.0</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="AN28" s="3">
         <v>2.0</v>
@@ -6652,7 +7096,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>86</v>
@@ -6672,7 +7116,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>86</v>
@@ -6692,7 +7136,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>86</v>
@@ -6721,7 +7165,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>86</v>
@@ -6750,7 +7194,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>86</v>
@@ -6810,7 +7254,7 @@
         <v>0.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AN33" s="3">
         <v>2.0</v>
@@ -6842,7 +7286,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>97</v>
@@ -6854,7 +7298,7 @@
         <v>55</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>126</v>
@@ -6862,7 +7306,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>97</v>
@@ -6882,7 +7326,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>97</v>
@@ -6911,7 +7355,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>97</v>
@@ -6920,7 +7364,7 @@
         <v>81</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>51</v>
@@ -6940,7 +7384,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>97</v>
@@ -7003,7 +7447,7 @@
         <v>0.0</v>
       </c>
       <c r="AM38" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AN38" s="3">
         <v>2.0</v>
@@ -7035,7 +7479,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>103</v>
@@ -7055,7 +7499,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>103</v>
@@ -7075,7 +7519,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>103</v>
@@ -7104,7 +7548,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>103</v>
@@ -7167,7 +7611,7 @@
         <v>4.0</v>
       </c>
       <c r="AM42" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AN42" s="3">
         <v>1.0</v>
@@ -7199,7 +7643,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>108</v>
@@ -7219,7 +7663,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>108</v>
@@ -7239,7 +7683,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>108</v>
@@ -7259,7 +7703,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>108</v>
@@ -7282,7 +7726,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>108</v>
@@ -7345,7 +7789,7 @@
         <v>3.0</v>
       </c>
       <c r="AM47" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AN47" s="3">
         <v>0.0</v>
@@ -7377,7 +7821,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>49</v>
@@ -7397,7 +7841,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
@@ -7417,7 +7861,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
@@ -7437,7 +7881,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
@@ -7466,7 +7910,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -7495,7 +7939,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
@@ -7552,7 +7996,7 @@
         <v>3.0</v>
       </c>
       <c r="AM53" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AN53" s="3">
         <v>2.0</v>
@@ -7584,7 +8028,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>68</v>
@@ -7604,7 +8048,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>68</v>
@@ -7624,7 +8068,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>68</v>
@@ -7653,7 +8097,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>68</v>
@@ -7662,7 +8106,7 @@
         <v>81</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>119</v>
@@ -7682,7 +8126,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>68</v>
@@ -7777,7 +8221,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>76</v>
@@ -7797,7 +8241,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>76</v>
@@ -7817,7 +8261,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>76</v>
@@ -7837,7 +8281,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>76</v>
@@ -7860,7 +8304,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>76</v>
@@ -7926,7 +8370,7 @@
         <v>2.0</v>
       </c>
       <c r="AM63" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AN63" s="3">
         <v>0.0</v>
@@ -7958,7 +8402,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>86</v>
@@ -7978,7 +8422,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>86</v>
@@ -7998,7 +8442,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>86</v>
@@ -8027,7 +8471,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>86</v>
@@ -8056,7 +8500,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>86</v>
@@ -8113,7 +8557,7 @@
         <v>1.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AN68" s="3">
         <v>2.0</v>
@@ -8145,7 +8589,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>97</v>
@@ -8165,7 +8609,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>97</v>
@@ -8185,7 +8629,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>97</v>
@@ -8200,7 +8644,7 @@
         <v>141</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M71" s="3">
         <v>2.0</v>
@@ -8214,13 +8658,13 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>59</v>
@@ -8237,7 +8681,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>97</v>
@@ -8297,7 +8741,7 @@
         <v>4.0</v>
       </c>
       <c r="AM73" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AN73" s="3">
         <v>1.0</v>
@@ -8329,7 +8773,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>103</v>
@@ -8349,7 +8793,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>103</v>
@@ -8369,7 +8813,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>103</v>
@@ -8398,7 +8842,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>103</v>
@@ -8452,7 +8896,7 @@
         <v>3.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AN77" s="3">
         <v>1.0</v>
@@ -8484,7 +8928,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>108</v>
@@ -8504,7 +8948,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>108</v>
@@ -8524,7 +8968,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>108</v>
@@ -8536,7 +8980,7 @@
         <v>59</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>136</v>
@@ -8553,7 +8997,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>108</v>
@@ -8576,7 +9020,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>108</v>
@@ -8642,7 +9086,7 @@
         <v>2.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AN82" s="3">
         <v>1.0</v>
@@ -8674,7 +9118,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>49</v>
@@ -8686,7 +9130,7 @@
         <v>135</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>61</v>
@@ -8694,7 +9138,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>49</v>
@@ -8714,7 +9158,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>49</v>
@@ -8723,7 +9167,7 @@
         <v>50</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>70</v>
@@ -8734,7 +9178,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>49</v>
@@ -8746,7 +9190,7 @@
         <v>59</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>99</v>
@@ -8763,7 +9207,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -8792,7 +9236,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
@@ -8821,7 +9265,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -8884,7 +9328,7 @@
         <v>0.0</v>
       </c>
       <c r="AM89" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AN89" s="3">
         <v>3.0</v>
@@ -8916,7 +9360,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>68</v>
@@ -8936,7 +9380,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>68</v>
@@ -8969,7 +9413,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>68</v>
@@ -8985,7 +9429,7 @@
         <v>59</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>99</v>
@@ -9002,7 +9446,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>68</v>
@@ -9015,7 +9459,7 @@
         <v>81</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>141</v>
@@ -9035,7 +9479,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>68</v>
@@ -9062,7 +9506,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>68</v>
@@ -9132,7 +9576,7 @@
         <v>8.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="AN95" s="3">
         <v>3.0</v>
@@ -9164,7 +9608,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>76</v>
@@ -9184,7 +9628,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>76</v>
@@ -9204,7 +9648,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>76</v>
@@ -9224,7 +9668,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
@@ -9239,7 +9683,7 @@
         <v>141</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M99" s="3">
         <v>10.0</v>
@@ -9253,7 +9697,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>76</v>
@@ -9276,7 +9720,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>76</v>
@@ -9342,7 +9786,7 @@
         <v>3.0</v>
       </c>
       <c r="AM101" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AN101" s="3">
         <v>1.0</v>
@@ -9374,7 +9818,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>86</v>
@@ -9394,7 +9838,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>86</v>
@@ -9423,7 +9867,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>86</v>
@@ -9446,7 +9890,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>86</v>
@@ -9509,7 +9953,7 @@
         <v>4.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AN105" s="3">
         <v>1.0</v>
@@ -9541,7 +9985,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>97</v>
@@ -9553,15 +9997,15 @@
         <v>51</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>97</v>
@@ -9575,7 +10019,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>97</v>
@@ -9595,13 +10039,13 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>51</v>
@@ -9615,7 +10059,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>97</v>
@@ -9644,7 +10088,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>97</v>
@@ -9667,7 +10111,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>97</v>
@@ -9730,7 +10174,7 @@
         <v>6.0</v>
       </c>
       <c r="AM112" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AN112" s="3">
         <v>1.0</v>
@@ -9762,7 +10206,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>103</v>
@@ -9771,7 +10215,7 @@
         <v>91</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>93</v>
@@ -9782,7 +10226,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>103</v>
@@ -9802,7 +10246,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>103</v>
@@ -9822,7 +10266,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>103</v>
@@ -9851,7 +10295,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>103</v>
@@ -9871,7 +10315,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>103</v>
@@ -9931,7 +10375,7 @@
         <v>1.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AN118" s="3">
         <v>1.0</v>
@@ -9963,7 +10407,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>108</v>
@@ -9983,7 +10427,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>108</v>
@@ -10003,7 +10447,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>108</v>
@@ -10023,7 +10467,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>108</v>
@@ -10046,7 +10490,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>108</v>
@@ -10075,7 +10519,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>108</v>
@@ -10138,7 +10582,7 @@
         <v>1.0</v>
       </c>
       <c r="AM124" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AN124" s="3">
         <v>1.0</v>
@@ -10170,7 +10614,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>49</v>
@@ -10190,7 +10634,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>49</v>
@@ -10210,7 +10654,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>49</v>
@@ -10239,7 +10683,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>49</v>
@@ -10268,7 +10712,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>49</v>
@@ -10277,7 +10721,7 @@
         <v>58</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>117</v>
@@ -10291,7 +10735,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>49</v>
@@ -10314,7 +10758,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>49</v>
@@ -10380,7 +10824,7 @@
         <v>13.0</v>
       </c>
       <c r="AM131" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AN131" s="3">
         <v>2.0</v>
@@ -10412,7 +10856,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>68</v>
@@ -10432,7 +10876,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>68</v>
@@ -10452,7 +10896,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>68</v>
@@ -10481,7 +10925,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>68</v>
@@ -10510,7 +10954,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>68</v>
@@ -10539,7 +10983,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>68</v>
@@ -10602,7 +11046,7 @@
         <v>0.0</v>
       </c>
       <c r="AM137" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AN137" s="3">
         <v>3.0</v>
@@ -10634,7 +11078,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>76</v>
@@ -10654,7 +11098,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>76</v>
@@ -10674,7 +11118,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>76</v>
@@ -10686,7 +11130,7 @@
         <v>55</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>126</v>
@@ -10694,7 +11138,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>76</v>
@@ -10723,7 +11167,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>76</v>
@@ -10752,7 +11196,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>76</v>
@@ -10815,7 +11259,7 @@
         <v>2.0</v>
       </c>
       <c r="AM143" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AN143" s="3">
         <v>2.0</v>
@@ -10847,7 +11291,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>86</v>
@@ -10867,7 +11311,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>86</v>
@@ -10887,7 +11331,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>86</v>
@@ -10899,7 +11343,7 @@
         <v>56</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>52</v>
@@ -10907,7 +11351,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>86</v>
@@ -10927,7 +11371,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>86</v>
@@ -10956,7 +11400,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>86</v>
@@ -10985,7 +11429,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>86</v>
@@ -11045,7 +11489,7 @@
         <v>0.0</v>
       </c>
       <c r="AM150" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AN150" s="3">
         <v>2.0</v>
@@ -11077,7 +11521,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>97</v>
@@ -11097,7 +11541,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>97</v>
@@ -11117,7 +11561,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>97</v>
@@ -11146,7 +11590,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>97</v>
@@ -11175,7 +11619,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>97</v>
@@ -11238,7 +11682,7 @@
         <v>1.0</v>
       </c>
       <c r="AM155" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AN155" s="3">
         <v>2.0</v>
@@ -11270,7 +11714,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>103</v>
@@ -11290,7 +11734,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>103</v>
@@ -11310,7 +11754,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>103</v>
@@ -11330,7 +11774,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>103</v>
@@ -11359,7 +11803,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>103</v>
@@ -11422,7 +11866,7 @@
         <v>0.0</v>
       </c>
       <c r="AM160" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AN160" s="3">
         <v>1.0</v>
@@ -11454,7 +11898,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>108</v>
@@ -11474,7 +11918,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>108</v>
@@ -11494,7 +11938,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>108</v>
@@ -11517,7 +11961,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>108</v>
@@ -11540,7 +11984,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>108</v>
@@ -11569,7 +12013,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>108</v>
@@ -11632,7 +12076,7 @@
         <v>3.0</v>
       </c>
       <c r="AM166" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AN166" s="3">
         <v>1.0</v>
@@ -11822,7 +12266,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>76</v>
@@ -11842,7 +12286,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>76</v>
@@ -11862,7 +12306,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>76</v>
@@ -11891,7 +12335,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>76</v>
@@ -11920,7 +12364,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>76</v>
@@ -11980,7 +12424,7 @@
         <v>9.0</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AN6" s="3">
         <v>2.0</v>
@@ -12012,7 +12456,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>86</v>
@@ -12032,13 +12476,13 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>82</v>
@@ -12052,13 +12496,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>64</v>
@@ -12072,7 +12516,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>86</v>
@@ -12101,7 +12545,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>86</v>
@@ -12130,7 +12574,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>86</v>
@@ -12142,7 +12586,7 @@
         <v>54</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S12" s="3">
         <v>7559.0</v>
@@ -12190,7 +12634,7 @@
         <v>4.0</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AN12" s="3">
         <v>2.0</v>
@@ -12222,13 +12666,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>51</v>
@@ -12242,7 +12686,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>97</v>
@@ -12262,7 +12706,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>97</v>
@@ -12291,7 +12735,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>97</v>
@@ -12320,7 +12764,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>97</v>
@@ -12349,7 +12793,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>97</v>
@@ -12361,7 +12805,7 @@
         <v>77</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S18" s="3">
         <v>8733.0</v>
@@ -12409,7 +12853,7 @@
         <v>4.0</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AN18" s="3">
         <v>3.0</v>
@@ -12441,7 +12885,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>103</v>
@@ -12461,7 +12905,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>103</v>
@@ -12481,7 +12925,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>103</v>
@@ -12510,7 +12954,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>103</v>
@@ -12533,7 +12977,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>103</v>
@@ -12593,7 +13037,7 @@
         <v>0.0</v>
       </c>
       <c r="AM23" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AN23" s="3">
         <v>1.0</v>
@@ -12625,7 +13069,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>108</v>
@@ -12645,7 +13089,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>108</v>
@@ -12665,7 +13109,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>108</v>
@@ -12677,21 +13121,21 @@
         <v>92</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>51</v>
@@ -12714,7 +13158,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>108</v>
@@ -12743,7 +13187,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>108</v>
@@ -12803,7 +13247,7 @@
         <v>1.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AN29" s="3">
         <v>2.0</v>
@@ -12835,7 +13279,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>49</v>
@@ -12855,13 +13299,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>51</v>
@@ -12875,7 +13319,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>49</v>
@@ -12895,7 +13339,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
@@ -12907,7 +13351,7 @@
         <v>59</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>126</v>
@@ -12924,7 +13368,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -12953,7 +13397,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
@@ -12982,13 +13426,13 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>100</v>
@@ -13011,7 +13455,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -13074,7 +13518,7 @@
         <v>2.0</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AN37" s="3">
         <v>4.0</v>
@@ -13106,7 +13550,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>68</v>
@@ -13126,7 +13570,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>68</v>
@@ -13146,13 +13590,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>51</v>
@@ -13166,7 +13610,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>68</v>
@@ -13178,7 +13622,7 @@
         <v>59</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>136</v>
@@ -13195,7 +13639,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>68</v>
@@ -13224,13 +13668,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>64</v>
@@ -13253,7 +13697,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>68</v>
@@ -13313,7 +13757,7 @@
         <v>0.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN44" s="3">
         <v>3.0</v>
@@ -13345,7 +13789,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>76</v>
@@ -13365,7 +13809,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>76</v>
@@ -13394,7 +13838,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>76</v>
@@ -13423,7 +13867,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>76</v>
@@ -13483,7 +13927,7 @@
         <v>0.0</v>
       </c>
       <c r="AM48" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AN48" s="3">
         <v>2.0</v>
@@ -13515,7 +13959,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>86</v>
@@ -13535,7 +13979,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>86</v>
@@ -13555,7 +13999,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>86</v>
@@ -13575,7 +14019,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>86</v>
@@ -13604,7 +14048,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>86</v>
@@ -13627,7 +14071,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>86</v>
@@ -13690,7 +14134,7 @@
         <v>1.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AN54" s="3">
         <v>1.0</v>
@@ -13722,7 +14166,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>97</v>
@@ -13742,13 +14186,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>51</v>
@@ -13762,19 +14206,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>52</v>
@@ -13782,7 +14226,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>97</v>
@@ -13811,7 +14255,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>97</v>
@@ -13823,7 +14267,7 @@
         <v>109</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S59" s="3">
         <v>7771.0</v>
@@ -13871,7 +14315,7 @@
         <v>3.0</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AN59" s="3">
         <v>1.0</v>
@@ -13903,13 +14347,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>51</v>
@@ -13923,7 +14367,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>103</v>
@@ -13943,7 +14387,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>103</v>
@@ -13972,7 +14416,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>103</v>
@@ -13984,7 +14428,7 @@
         <v>77</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S63" s="3">
         <v>9627.0</v>
@@ -14032,7 +14476,7 @@
         <v>3.0</v>
       </c>
       <c r="AM63" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AN63" s="3">
         <v>1.0</v>
@@ -14064,7 +14508,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>108</v>
@@ -14084,7 +14528,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>108</v>
@@ -14104,7 +14548,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>108</v>
@@ -14124,13 +14568,13 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>51</v>
@@ -14153,7 +14597,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>108</v>
@@ -14182,7 +14626,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>108</v>
@@ -14242,7 +14686,7 @@
         <v>3.0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AN69" s="3">
         <v>2.0</v>
@@ -14274,7 +14718,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>49</v>
@@ -14294,7 +14738,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>49</v>
@@ -14314,7 +14758,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>49</v>
@@ -14343,13 +14787,13 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>51</v>
@@ -14372,13 +14816,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>59</v>
@@ -14395,7 +14839,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>49</v>
@@ -14424,7 +14868,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>49</v>
@@ -14484,7 +14928,7 @@
         <v>0.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AN76" s="3">
         <v>3.0</v>
@@ -14516,7 +14960,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>68</v>
@@ -14536,7 +14980,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>68</v>
@@ -14556,13 +15000,13 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>51</v>
@@ -14576,13 +15020,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>51</v>
@@ -14605,7 +15049,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>68</v>
@@ -14634,7 +15078,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>68</v>
@@ -14663,7 +15107,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>68</v>
@@ -14738,7 +15182,7 @@
         <v>1.0</v>
       </c>
       <c r="AM83" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AN83" s="3">
         <v>3.0</v>
@@ -14770,7 +15214,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>76</v>
@@ -14790,7 +15234,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>76</v>
@@ -14810,13 +15254,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>51</v>
@@ -14839,7 +15283,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>76</v>
@@ -14868,7 +15312,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>76</v>
@@ -14928,7 +15372,7 @@
         <v>1.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AN88" s="3">
         <v>2.0</v>
@@ -14960,7 +15404,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>86</v>
@@ -14980,7 +15424,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>86</v>
@@ -15000,7 +15444,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>86</v>
@@ -15029,7 +15473,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>86</v>
@@ -15044,7 +15488,7 @@
         <v>51</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M92" s="3">
         <v>3.0</v>
@@ -15058,7 +15502,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>86</v>
@@ -15118,7 +15562,7 @@
         <v>0.0</v>
       </c>
       <c r="AM93" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AN93" s="3">
         <v>2.0</v>
@@ -15150,7 +15594,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>97</v>
@@ -15170,7 +15614,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>97</v>
@@ -15190,7 +15634,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>97</v>
@@ -15210,13 +15654,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>51</v>
@@ -15239,7 +15683,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>97</v>
@@ -15268,7 +15712,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>97</v>
@@ -15328,7 +15772,7 @@
         <v>0.0</v>
       </c>
       <c r="AM99" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AN99" s="3">
         <v>2.0</v>
@@ -15360,7 +15804,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>103</v>
@@ -15380,13 +15824,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>51</v>
@@ -15400,7 +15844,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>103</v>
@@ -15420,7 +15864,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>103</v>
@@ -15449,7 +15893,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>103</v>
@@ -15461,7 +15905,7 @@
         <v>77</v>
       </c>
       <c r="R104" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S104" s="3">
         <v>8098.0</v>
@@ -15512,7 +15956,7 @@
         <v>2.0</v>
       </c>
       <c r="AM104" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AN104" s="3">
         <v>1.0</v>
@@ -15544,7 +15988,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>108</v>
@@ -15564,13 +16008,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>64</v>
@@ -15584,7 +16028,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>108</v>
@@ -15604,13 +16048,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>59</v>
@@ -15633,7 +16077,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>108</v>
@@ -15645,7 +16089,7 @@
         <v>56</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>52</v>
@@ -15656,7 +16100,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>108</v>
@@ -15668,7 +16112,7 @@
         <v>77</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S110" s="3">
         <v>13542.0</v>
@@ -15722,7 +16166,7 @@
         <v>7.0</v>
       </c>
       <c r="AM110" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AN110" s="3">
         <v>1.0</v>
@@ -15754,7 +16198,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>49</v>
@@ -15774,7 +16218,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>49</v>
@@ -15794,7 +16238,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>49</v>
@@ -15814,13 +16258,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>73</v>
@@ -15831,7 +16275,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>49</v>
@@ -15860,7 +16304,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>49</v>
@@ -15889,7 +16333,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>49</v>
@@ -15918,7 +16362,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>49</v>
@@ -15984,7 +16428,7 @@
         <v>3.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AN118" s="3">
         <v>3.0</v>
@@ -16016,7 +16460,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>68</v>
@@ -16036,7 +16480,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>68</v>
@@ -16056,7 +16500,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>68</v>
@@ -16076,13 +16520,13 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>144</v>
@@ -16096,7 +16540,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>68</v>
@@ -16125,7 +16569,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>68</v>
@@ -16154,7 +16598,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>68</v>
@@ -16183,7 +16627,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>68</v>
@@ -16243,7 +16687,7 @@
         <v>1.0</v>
       </c>
       <c r="AM126" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AN126" s="3">
         <v>3.0</v>
@@ -16275,7 +16719,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>76</v>
@@ -16295,7 +16739,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>76</v>
@@ -16315,7 +16759,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>76</v>
@@ -16338,7 +16782,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>76</v>
@@ -16398,7 +16842,7 @@
         <v>1.0</v>
       </c>
       <c r="AM130" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AN130" s="3">
         <v>0.0</v>
@@ -16430,13 +16874,13 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>55</v>
@@ -16450,13 +16894,13 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>51</v>
@@ -16470,7 +16914,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>86</v>
@@ -16499,7 +16943,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>86</v>
@@ -16508,10 +16952,10 @@
         <v>2.0</v>
       </c>
       <c r="Q134" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R134" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S134" s="3">
         <v>5581.0</v>
@@ -16559,7 +17003,7 @@
         <v>3.0</v>
       </c>
       <c r="AM134" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AN134" s="3">
         <v>1.0</v>
@@ -16591,7 +17035,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>97</v>
@@ -16611,7 +17055,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>97</v>
@@ -16631,13 +17075,13 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>59</v>
@@ -16660,7 +17104,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>97</v>
@@ -16689,7 +17133,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>97</v>
@@ -16718,7 +17162,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>97</v>
@@ -16778,7 +17222,7 @@
         <v>0.0</v>
       </c>
       <c r="AM140" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AN140" s="3">
         <v>3.0</v>
@@ -16810,7 +17254,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>103</v>
@@ -16830,13 +17274,13 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>56</v>
@@ -16850,7 +17294,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>103</v>
@@ -16859,18 +17303,18 @@
         <v>104</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>103</v>
@@ -16899,7 +17343,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>103</v>
@@ -16928,7 +17372,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>103</v>
@@ -16940,7 +17384,7 @@
         <v>54</v>
       </c>
       <c r="R146" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S146" s="3">
         <v>6595.0</v>
@@ -16988,7 +17432,7 @@
         <v>2.0</v>
       </c>
       <c r="AM146" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AN146" s="3">
         <v>2.0</v>
@@ -17020,7 +17464,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>108</v>
@@ -17040,13 +17484,13 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>55</v>
@@ -17060,7 +17504,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>108</v>
@@ -17080,7 +17524,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>108</v>
@@ -17103,13 +17547,13 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I151" s="2" t="s">
         <v>59</v>
@@ -17126,7 +17570,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>108</v>
@@ -17135,7 +17579,7 @@
         <v>2.0</v>
       </c>
       <c r="Q152" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R152" s="1" t="s">
         <v>109</v>
@@ -17192,7 +17636,7 @@
         <v>2.0</v>
       </c>
       <c r="AM152" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AN152" s="3">
         <v>0.0</v>
@@ -17224,7 +17668,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>49</v>
@@ -17244,7 +17688,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>49</v>
@@ -17264,7 +17708,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>49</v>
@@ -17284,7 +17728,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>49</v>
@@ -17313,7 +17757,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>49</v>
@@ -17342,7 +17786,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>49</v>
@@ -17371,7 +17815,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>49</v>
@@ -17425,7 +17869,7 @@
         <v>1.0</v>
       </c>
       <c r="AM159" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AN159" s="3">
         <v>3.0</v>
@@ -17457,7 +17901,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>68</v>
@@ -17477,7 +17921,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>68</v>
@@ -17497,7 +17941,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>68</v>
@@ -17517,7 +17961,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>68</v>
@@ -17537,7 +17981,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>68</v>
@@ -17566,7 +18010,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>68</v>
@@ -17595,7 +18039,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>68</v>
@@ -17652,7 +18096,7 @@
         <v>1.0</v>
       </c>
       <c r="AM166" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AN166" s="3">
         <v>2.0</v>
@@ -17684,7 +18128,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>76</v>
@@ -17704,7 +18148,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>76</v>
@@ -17724,7 +18168,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>76</v>
@@ -17744,7 +18188,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>76</v>
@@ -17773,7 +18217,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>76</v>
@@ -17802,7 +18246,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>76</v>
@@ -17862,7 +18306,7 @@
         <v>4.0</v>
       </c>
       <c r="AM172" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AN172" s="3">
         <v>2.0</v>
@@ -17894,7 +18338,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>86</v>
@@ -17914,7 +18358,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>86</v>
@@ -17934,7 +18378,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>86</v>
@@ -17963,7 +18407,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>86</v>
@@ -17992,7 +18436,7 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>86</v>
@@ -18055,7 +18499,7 @@
         <v>3.0</v>
       </c>
       <c r="AM177" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AN177" s="3">
         <v>2.0</v>
@@ -18087,7 +18531,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>97</v>
@@ -18107,7 +18551,7 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>97</v>
@@ -18127,7 +18571,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>97</v>
@@ -18150,13 +18594,13 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I181" s="2" t="s">
         <v>59</v>
@@ -18179,7 +18623,7 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>97</v>
@@ -18233,7 +18677,7 @@
         <v>3.0</v>
       </c>
       <c r="AM182" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AN182" s="3">
         <v>1.0</v>
@@ -18423,7 +18867,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>76</v>
@@ -18443,7 +18887,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>76</v>
@@ -18466,7 +18910,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>76</v>
@@ -18495,7 +18939,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>76</v>
@@ -18518,7 +18962,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>76</v>
@@ -18581,7 +19025,7 @@
         <v>1.0</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="AN6" s="3">
         <v>1.0</v>
@@ -18613,7 +19057,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>86</v>
@@ -18633,13 +19077,13 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>51</v>
@@ -18653,7 +19097,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>86</v>
@@ -18682,7 +19126,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>86</v>
@@ -18705,7 +19149,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>86</v>
@@ -18728,7 +19172,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>86</v>
@@ -18740,7 +19184,7 @@
         <v>54</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S12" s="3">
         <v>17596.75</v>
@@ -18788,7 +19232,7 @@
         <v>1.0</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="AN12" s="3">
         <v>1.0</v>
@@ -18820,13 +19264,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>51</v>
@@ -18840,7 +19284,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>97</v>
@@ -18860,7 +19304,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>97</v>
@@ -18880,7 +19324,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>97</v>
@@ -18909,7 +19353,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>97</v>
@@ -18921,7 +19365,7 @@
         <v>77</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S17" s="3">
         <v>15189.699999999997</v>
@@ -18969,7 +19413,7 @@
         <v>2.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AN17" s="3">
         <v>1.0</v>
@@ -19001,13 +19445,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>55</v>
@@ -19021,7 +19465,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>103</v>
@@ -19041,7 +19485,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>103</v>
@@ -19061,7 +19505,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>103</v>
@@ -19076,7 +19520,7 @@
         <v>98</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="M21" s="3">
         <v>14.0</v>
@@ -19090,7 +19534,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>103</v>
@@ -19102,7 +19546,7 @@
         <v>51</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>98</v>
@@ -19110,7 +19554,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>103</v>
@@ -19119,7 +19563,7 @@
         <v>0.0</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>109</v>
@@ -19205,7 +19649,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>108</v>
@@ -19225,7 +19669,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>108</v>
@@ -19245,7 +19689,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>108</v>
@@ -19265,7 +19709,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>108</v>
@@ -19294,13 +19738,13 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>59</v>
@@ -19317,7 +19761,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>108</v>
@@ -19380,7 +19824,7 @@
         <v>2.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AN29" s="3">
         <v>1.0</v>
@@ -19412,7 +19856,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>49</v>
@@ -19432,7 +19876,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>49</v>
@@ -19452,7 +19896,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>49</v>
@@ -19472,13 +19916,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>51</v>
@@ -19501,7 +19945,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -19530,7 +19974,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
@@ -19559,7 +20003,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -19582,7 +20026,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -19602,7 +20046,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>49</v>
@@ -19662,7 +20106,7 @@
         <v>1.0</v>
       </c>
       <c r="AM38" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AN38" s="3">
         <v>3.0</v>
@@ -19694,7 +20138,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>68</v>
@@ -19706,15 +20150,15 @@
         <v>64</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>68</v>
@@ -19726,7 +20170,7 @@
         <v>56</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>136</v>
@@ -19734,7 +20178,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>68</v>
@@ -19754,13 +20198,13 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>51</v>
@@ -19783,7 +20227,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>68</v>
@@ -19812,7 +20256,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>68</v>
@@ -19835,7 +20279,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>68</v>
@@ -19895,7 +20339,7 @@
         <v>3.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AN45" s="3">
         <v>2.0</v>
@@ -19927,7 +20371,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>76</v>
@@ -19947,7 +20391,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>76</v>
@@ -19967,7 +20411,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>76</v>
@@ -19987,7 +20431,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>76</v>
@@ -20007,13 +20451,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>144</v>
@@ -20036,7 +20480,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>76</v>
@@ -20065,7 +20509,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>76</v>
@@ -20125,7 +20569,7 @@
         <v>2.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AN52" s="3">
         <v>2.0</v>
@@ -20157,7 +20601,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>86</v>
@@ -20177,7 +20621,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>86</v>
@@ -20186,7 +20630,7 @@
         <v>109</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>100</v>
@@ -20197,13 +20641,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>64</v>
@@ -20217,7 +20661,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>86</v>
@@ -20232,7 +20676,7 @@
         <v>98</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="M56" s="3">
         <v>11.0</v>
@@ -20246,7 +20690,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>86</v>
@@ -20275,7 +20719,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>86</v>
@@ -20370,7 +20814,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>97</v>
@@ -20390,13 +20834,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>51</v>
@@ -20410,7 +20854,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>97</v>
@@ -20422,15 +20866,15 @@
         <v>51</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>97</v>
@@ -20459,7 +20903,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>97</v>
@@ -20488,7 +20932,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>97</v>
@@ -20545,7 +20989,7 @@
         <v>2.0</v>
       </c>
       <c r="AM64" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AN64" s="3">
         <v>2.0</v>
@@ -20577,7 +21021,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>103</v>
@@ -20597,13 +21041,13 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>51</v>
@@ -20617,7 +21061,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>103</v>
@@ -20637,7 +21081,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>103</v>
@@ -20666,13 +21110,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>56</v>
@@ -20689,7 +21133,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>103</v>
@@ -20752,7 +21196,7 @@
         <v>0.0</v>
       </c>
       <c r="AM70" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AN70" s="3">
         <v>1.0</v>
@@ -20784,7 +21228,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>108</v>
@@ -20804,13 +21248,13 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>55</v>
@@ -20824,7 +21268,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>108</v>
@@ -20844,7 +21288,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>108</v>
@@ -20873,13 +21317,13 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>59</v>
@@ -20896,7 +21340,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>108</v>
@@ -20905,7 +21349,7 @@
         <v>1.0</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R76" s="1" t="s">
         <v>109</v>
@@ -20956,7 +21400,7 @@
         <v>7.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AN76" s="3">
         <v>1.0</v>
@@ -20988,7 +21432,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>49</v>
@@ -21008,13 +21452,13 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>51</v>
@@ -21028,7 +21472,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>49</v>
@@ -21048,7 +21492,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>49</v>
@@ -21068,7 +21512,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>49</v>
@@ -21080,7 +21524,7 @@
         <v>59</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>53</v>
@@ -21097,7 +21541,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>49</v>
@@ -21126,7 +21570,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>49</v>
@@ -21155,7 +21599,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>49</v>
@@ -21215,7 +21659,7 @@
         <v>2.0</v>
       </c>
       <c r="AM84" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AN84" s="3">
         <v>3.0</v>
@@ -21247,7 +21691,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>68</v>
@@ -21267,7 +21711,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>68</v>
@@ -21287,7 +21731,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>68</v>
@@ -21307,7 +21751,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>68</v>
@@ -21336,13 +21780,13 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>59</v>
@@ -21365,7 +21809,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>68</v>
@@ -21374,7 +21818,7 @@
         <v>81</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>71</v>
@@ -21394,7 +21838,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>68</v>
@@ -21457,7 +21901,7 @@
         <v>2.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AN91" s="3">
         <v>3.0</v>
@@ -21489,7 +21933,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>76</v>
@@ -21509,7 +21953,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>76</v>
@@ -21529,13 +21973,13 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>64</v>
@@ -21549,7 +21993,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>76</v>
@@ -21569,7 +22013,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>76</v>
@@ -21598,7 +22042,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>76</v>
@@ -21621,13 +22065,13 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>51</v>
@@ -21650,7 +22094,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
@@ -21713,7 +22157,7 @@
         <v>1.0</v>
       </c>
       <c r="AM99" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AN99" s="3">
         <v>2.0</v>
@@ -21745,7 +22189,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>86</v>
@@ -21765,13 +22209,13 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>82</v>
@@ -21785,7 +22229,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>86</v>
@@ -21797,15 +22241,15 @@
         <v>56</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>86</v>
@@ -21834,13 +22278,13 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>59</v>
@@ -21857,7 +22301,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>86</v>
@@ -21869,7 +22313,7 @@
         <v>54</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S105" s="3">
         <v>8451.0</v>
@@ -21920,7 +22364,7 @@
         <v>3.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AN105" s="3">
         <v>1.0</v>
@@ -21952,7 +22396,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>97</v>
@@ -21975,7 +22419,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>97</v>
@@ -21995,13 +22439,13 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>82</v>
@@ -22024,7 +22468,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>97</v>
@@ -22053,7 +22497,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>97</v>
@@ -22082,7 +22526,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>97</v>
@@ -22177,7 +22621,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>103</v>
@@ -22197,13 +22641,13 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>55</v>
@@ -22217,13 +22661,13 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>51</v>
@@ -22237,7 +22681,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>103</v>
@@ -22266,7 +22710,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>103</v>
@@ -22275,7 +22719,7 @@
         <v>0.0</v>
       </c>
       <c r="Q116" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R116" s="1" t="s">
         <v>54</v>
@@ -22326,7 +22770,7 @@
         <v>0.0</v>
       </c>
       <c r="AM116" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AN116" s="3">
         <v>1.0</v>
@@ -22358,7 +22802,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>108</v>
@@ -22378,7 +22822,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>108</v>
@@ -22398,7 +22842,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>108</v>
@@ -22418,7 +22862,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>108</v>
@@ -22438,13 +22882,13 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>82</v>
@@ -22467,13 +22911,13 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>59</v>
@@ -22490,7 +22934,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>108</v>
@@ -22556,7 +23000,7 @@
         <v>3.0</v>
       </c>
       <c r="AM123" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AN123" s="3">
         <v>1.0</v>
@@ -22588,7 +23032,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>49</v>
@@ -22608,7 +23052,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>49</v>
@@ -22628,7 +23072,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>49</v>
@@ -22661,7 +23105,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>49</v>
@@ -22694,7 +23138,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>49</v>
@@ -22727,7 +23171,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>49</v>
@@ -22794,7 +23238,7 @@
         <v>2.0</v>
       </c>
       <c r="AM129" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AN129" s="3">
         <v>3.0</v>
@@ -22826,7 +23270,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>68</v>
@@ -22846,7 +23290,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>68</v>
@@ -22866,13 +23310,13 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>51</v>
@@ -22895,7 +23339,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>68</v>
@@ -22924,7 +23368,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>68</v>
@@ -22953,7 +23397,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>68</v>
@@ -23013,7 +23457,7 @@
         <v>1.0</v>
       </c>
       <c r="AM135" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AN135" s="3">
         <v>3.0</v>
@@ -23045,7 +23489,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>76</v>
@@ -23065,7 +23509,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>76</v>
@@ -23085,7 +23529,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>76</v>
@@ -23114,13 +23558,13 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>59</v>
@@ -23143,7 +23587,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>76</v>
@@ -23235,13 +23679,13 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>55</v>
@@ -23250,12 +23694,12 @@
         <v>98</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>86</v>
@@ -23284,7 +23728,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>86</v>
@@ -23307,7 +23751,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>86</v>
@@ -23316,10 +23760,10 @@
         <v>1.0</v>
       </c>
       <c r="Q144" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R144" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S144" s="3">
         <v>6531.0</v>
@@ -23370,7 +23814,7 @@
         <v>1.0</v>
       </c>
       <c r="AM144" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AN144" s="3">
         <v>1.0</v>
@@ -23402,7 +23846,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>97</v>
@@ -23422,13 +23866,13 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>51</v>
@@ -23445,13 +23889,13 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I147" s="2" t="s">
         <v>59</v>
@@ -23468,7 +23912,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>97</v>
@@ -23491,7 +23935,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>97</v>
@@ -23520,7 +23964,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>97</v>
@@ -23532,7 +23976,7 @@
         <v>91</v>
       </c>
       <c r="R150" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="S150" s="3">
         <v>9893.0</v>
@@ -23580,7 +24024,7 @@
         <v>5.0</v>
       </c>
       <c r="AM150" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AN150" s="3">
         <v>1.0</v>
@@ -23612,7 +24056,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>103</v>
@@ -23621,7 +24065,7 @@
         <v>109</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>93</v>
@@ -23632,13 +24076,13 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>120</v>
@@ -23652,7 +24096,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>103</v>
@@ -23681,13 +24125,13 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I154" s="2" t="s">
         <v>51</v>
@@ -23710,7 +24154,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>103</v>
@@ -23719,7 +24163,7 @@
         <v>0.0</v>
       </c>
       <c r="Q155" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R155" s="1" t="s">
         <v>109</v>
@@ -23770,7 +24214,7 @@
         <v>1.0</v>
       </c>
       <c r="AM155" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AN155" s="3">
         <v>2.0</v>
@@ -23802,7 +24246,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>108</v>
@@ -23822,7 +24266,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>108</v>
@@ -23842,7 +24286,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>108</v>
@@ -23871,7 +24315,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>108</v>
@@ -23900,7 +24344,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>108</v>
@@ -23929,7 +24373,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>108</v>
@@ -23989,7 +24433,7 @@
         <v>0.0</v>
       </c>
       <c r="AM161" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AN161" s="3">
         <v>3.0</v>
@@ -24021,7 +24465,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>49</v>
@@ -24041,7 +24485,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>49</v>
@@ -24061,7 +24505,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>49</v>
@@ -24090,7 +24534,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>49</v>
@@ -24113,7 +24557,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>49</v>
@@ -24142,7 +24586,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>49</v>
@@ -24202,7 +24646,7 @@
         <v>2.0</v>
       </c>
       <c r="AM167" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AN167" s="3">
         <v>2.0</v>
@@ -24234,7 +24678,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>68</v>
@@ -24254,7 +24698,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>68</v>
@@ -24274,7 +24718,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>68</v>
@@ -24294,7 +24738,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>68</v>
@@ -24314,13 +24758,13 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I172" s="2" t="s">
         <v>51</v>
@@ -24343,7 +24787,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>68</v>
@@ -24372,7 +24816,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>68</v>
@@ -24401,7 +24845,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>68</v>
@@ -24461,7 +24905,7 @@
         <v>10.0</v>
       </c>
       <c r="AM175" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AN175" s="3">
         <v>3.0</v>
@@ -24651,7 +25095,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>108</v>
@@ -24671,7 +25115,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>108</v>
@@ -24691,7 +25135,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>108</v>
@@ -24714,13 +25158,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>51</v>
@@ -24743,7 +25187,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>108</v>
@@ -24755,7 +25199,7 @@
         <v>59</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>136</v>
@@ -24772,7 +25216,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>108</v>
@@ -24832,7 +25276,7 @@
         <v>5.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -24864,7 +25308,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>49</v>
@@ -24884,13 +25328,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>59</v>
@@ -24913,16 +25357,16 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>52</v>
@@ -24942,7 +25386,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -25002,7 +25446,7 @@
         <v>1.0</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AN11" s="3">
         <v>2.0</v>
@@ -25034,7 +25478,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>68</v>
@@ -25054,7 +25498,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>68</v>
@@ -25083,13 +25527,13 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>51</v>
@@ -25112,7 +25556,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>68</v>
@@ -25172,7 +25616,7 @@
         <v>2.0</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AN15" s="3">
         <v>2.0</v>
@@ -25204,7 +25648,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>76</v>
@@ -25213,7 +25657,7 @@
         <v>109</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>117</v>
@@ -25224,7 +25668,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>76</v>
@@ -25236,7 +25680,7 @@
         <v>55</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>125</v>
@@ -25244,13 +25688,13 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>51</v>
@@ -25273,13 +25717,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>59</v>
@@ -25296,7 +25740,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>76</v>
@@ -25325,7 +25769,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>76</v>
@@ -25385,7 +25829,7 @@
         <v>0.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AN21" s="3">
         <v>2.0</v>
@@ -25417,13 +25861,13 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>55</v>
@@ -25437,7 +25881,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>86</v>
@@ -25457,7 +25901,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>86</v>
@@ -25477,7 +25921,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>86</v>
@@ -25506,13 +25950,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>59</v>
@@ -25529,7 +25973,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>86</v>
@@ -25558,7 +26002,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>86</v>
@@ -25567,7 +26011,7 @@
         <v>2.0</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>62</v>
@@ -25621,7 +26065,7 @@
         <v>1.0</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN28" s="3">
         <v>2.0</v>
@@ -25653,13 +26097,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>55</v>
@@ -25673,7 +26117,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>97</v>
@@ -25688,7 +26132,7 @@
         <v>119</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M30" s="3">
         <v>2.0</v>
@@ -25702,13 +26146,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>51</v>
@@ -25731,7 +26175,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>97</v>
@@ -25760,7 +26204,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>97</v>
@@ -25769,10 +26213,10 @@
         <v>1.0</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S33" s="3">
         <v>10147.0</v>
@@ -25820,7 +26264,7 @@
         <v>2.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AN33" s="3">
         <v>3.0</v>
@@ -25852,7 +26296,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>103</v>
@@ -25872,7 +26316,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>103</v>
@@ -25892,7 +26336,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>103</v>
@@ -25921,13 +26365,13 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>59</v>
@@ -25944,7 +26388,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>103</v>
@@ -25998,7 +26442,7 @@
         <v>3.0</v>
       </c>
       <c r="AM38" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AN38" s="3">
         <v>1.0</v>
@@ -26030,7 +26474,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>108</v>
@@ -26050,13 +26494,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>59</v>
@@ -26079,7 +26523,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>108</v>
@@ -26108,7 +26552,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>108</v>
@@ -26137,7 +26581,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>108</v>
@@ -26197,7 +26641,7 @@
         <v>0.0</v>
       </c>
       <c r="AM43" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AN43" s="3">
         <v>3.0</v>
@@ -26229,7 +26673,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>49</v>
@@ -26249,7 +26693,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>49</v>
@@ -26269,13 +26713,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>51</v>
@@ -26298,7 +26742,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>49</v>
@@ -26327,7 +26771,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>49</v>
@@ -26339,7 +26783,7 @@
         <v>51</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>126</v>
@@ -26356,7 +26800,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
@@ -26419,7 +26863,7 @@
         <v>5.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AN49" s="3">
         <v>3.0</v>
@@ -26451,7 +26895,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>68</v>
@@ -26471,7 +26915,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>68</v>
@@ -26491,13 +26935,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>60</v>
@@ -26520,7 +26964,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>68</v>
@@ -26549,7 +26993,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>68</v>
@@ -26572,7 +27016,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>68</v>
@@ -26664,7 +27108,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>76</v>
@@ -26684,7 +27128,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>76</v>
@@ -26704,7 +27148,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>76</v>
@@ -26727,7 +27171,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>76</v>
@@ -26756,7 +27200,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>76</v>
@@ -26785,7 +27229,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>76</v>
@@ -26845,7 +27289,7 @@
         <v>4.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AN61" s="3">
         <v>2.0</v>
@@ -26877,13 +27321,13 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>55</v>
@@ -26897,7 +27341,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>86</v>
@@ -26917,7 +27361,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>86</v>
@@ -26937,13 +27381,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>59</v>
@@ -26960,7 +27404,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>86</v>
@@ -26969,7 +27413,7 @@
         <v>1.0</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R66" s="1" t="s">
         <v>54</v>
@@ -27023,7 +27467,7 @@
         <v>2.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AN66" s="3">
         <v>0.0</v>
@@ -27055,7 +27499,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>97</v>
@@ -27075,7 +27519,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>97</v>
@@ -27095,13 +27539,13 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>51</v>
@@ -27124,7 +27568,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>97</v>
@@ -27153,7 +27597,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>97</v>
@@ -27213,7 +27657,7 @@
         <v>2.0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AN71" s="3">
         <v>2.0</v>
@@ -27245,7 +27689,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>103</v>
@@ -27265,7 +27709,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>103</v>
@@ -27280,18 +27724,18 @@
         <v>141</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>51</v>
@@ -27314,13 +27758,13 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>59</v>
@@ -27337,7 +27781,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>103</v>
@@ -27400,7 +27844,7 @@
         <v>3.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AN76" s="3">
         <v>1.0</v>
@@ -27432,7 +27876,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>108</v>
@@ -27452,7 +27896,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>108</v>
@@ -27472,7 +27916,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>108</v>
@@ -27501,13 +27945,13 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>59</v>
@@ -27524,7 +27968,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>108</v>
@@ -27587,7 +28031,7 @@
         <v>2.0</v>
       </c>
       <c r="AM81" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AN81" s="3">
         <v>1.0</v>
@@ -27619,13 +28063,13 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>51</v>
@@ -27639,7 +28083,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>49</v>
@@ -27659,7 +28103,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>49</v>
@@ -27679,7 +28123,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>49</v>
@@ -27699,7 +28143,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>49</v>
@@ -27728,7 +28172,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -27757,13 +28201,13 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>65</v>
@@ -27786,7 +28230,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -27798,7 +28242,7 @@
         <v>109</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S89" s="3">
         <v>17117.47</v>
@@ -27878,13 +28322,13 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>51</v>
@@ -27898,7 +28342,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>68</v>
@@ -27918,7 +28362,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>68</v>
@@ -27938,7 +28382,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>68</v>
@@ -27958,7 +28402,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>68</v>
@@ -27978,7 +28422,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>68</v>
@@ -28007,7 +28451,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>68</v>
@@ -28036,13 +28480,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>65</v>
@@ -28065,7 +28509,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>68</v>
@@ -28125,7 +28569,7 @@
         <v>0.0</v>
       </c>
       <c r="AM98" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AN98" s="3">
         <v>3.0</v>
@@ -28157,7 +28601,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
@@ -28177,7 +28621,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>76</v>
@@ -28197,7 +28641,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>76</v>
@@ -28226,7 +28670,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>76</v>
@@ -28255,7 +28699,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>76</v>
@@ -28278,7 +28722,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>76</v>
@@ -28341,7 +28785,7 @@
         <v>0.0</v>
       </c>
       <c r="AM104" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="AN104" s="3">
         <v>2.0</v>
@@ -28373,7 +28817,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>86</v>
@@ -28393,13 +28837,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>79</v>
@@ -28413,13 +28857,13 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>86</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>59</v>
@@ -28442,7 +28886,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>86</v>
@@ -28471,7 +28915,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>86</v>
@@ -28483,7 +28927,7 @@
         <v>54</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S109" s="3">
         <v>15208.229999999992</v>
@@ -28534,7 +28978,7 @@
         <v>1.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AN109" s="3">
         <v>2.0</v>
@@ -28566,7 +29010,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>97</v>
@@ -28586,13 +29030,13 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>55</v>
@@ -28606,13 +29050,13 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>51</v>
@@ -28635,13 +29079,13 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>59</v>
@@ -28658,7 +29102,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>97</v>
@@ -28667,7 +29111,7 @@
         <v>0.0</v>
       </c>
       <c r="Q114" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="R114" s="1" t="s">
         <v>54</v>
@@ -28718,7 +29162,7 @@
         <v>3.0</v>
       </c>
       <c r="AM114" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN114" s="3">
         <v>1.0</v>
@@ -28750,7 +29194,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>103</v>
@@ -28770,7 +29214,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>103</v>
@@ -28790,7 +29234,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>103</v>
@@ -28810,13 +29254,13 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>59</v>
@@ -28833,7 +29277,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>103</v>
@@ -28856,7 +29300,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>103</v>
@@ -28879,7 +29323,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>103</v>
@@ -28974,7 +29418,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>108</v>
@@ -28994,13 +29438,13 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>55</v>
@@ -29014,7 +29458,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>108</v>
@@ -29034,7 +29478,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>108</v>
@@ -29063,13 +29507,13 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>51</v>
@@ -29092,7 +29536,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>108</v>
@@ -29115,7 +29559,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>108</v>
@@ -29124,7 +29568,7 @@
         <v>2.0</v>
       </c>
       <c r="Q128" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="R128" s="1" t="s">
         <v>54</v>
@@ -29178,7 +29622,7 @@
         <v>2.0</v>
       </c>
       <c r="AM128" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AN128" s="3">
         <v>2.0</v>
@@ -29210,7 +29654,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>49</v>
@@ -29230,7 +29674,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>49</v>
@@ -29242,7 +29686,7 @@
         <v>55</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>120</v>
@@ -29250,7 +29694,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>49</v>
@@ -29270,13 +29714,13 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>59</v>
@@ -29299,7 +29743,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>49</v>
@@ -29328,7 +29772,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>49</v>
@@ -29391,7 +29835,7 @@
         <v>1.0</v>
       </c>
       <c r="AM134" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AN134" s="3">
         <v>2.0</v>
@@ -29423,7 +29867,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>68</v>
@@ -29443,7 +29887,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>68</v>
@@ -29463,13 +29907,13 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>51</v>
@@ -29492,7 +29936,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>68</v>
@@ -29521,13 +29965,13 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>68</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>59</v>
@@ -29544,7 +29988,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>68</v>
@@ -29607,7 +30051,7 @@
         <v>3.0</v>
       </c>
       <c r="AM140" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="AN140" s="3">
         <v>2.0</v>
@@ -29639,7 +30083,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>76</v>
@@ -29659,7 +30103,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>76</v>
@@ -29679,7 +30123,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>76</v>
@@ -29699,7 +30143,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>76</v>
@@ -29709,7 +30153,7 @@
       <c r="E144" s="1"/>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I144" s="2" t="s">
         <v>51</v>
@@ -29732,7 +30176,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>76</v>
@@ -29765,7 +30209,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>76</v>
@@ -29832,7 +30276,7 @@
         <v>0.0</v>
       </c>
       <c r="AM146" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AN146" s="3">
         <v>2.0</v>
@@ -29864,7 +30308,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>86</v>
@@ -29884,13 +30328,13 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>51</v>
@@ -29904,13 +30348,13 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>82</v>
@@ -29924,7 +30368,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>86</v>
@@ -29944,7 +30388,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>86</v>
@@ -29973,7 +30417,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>86</v>
@@ -30002,7 +30446,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>86</v>
@@ -30056,7 +30500,7 @@
         <v>0.0</v>
       </c>
       <c r="AM153" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AN153" s="3">
         <v>2.0</v>
@@ -30088,7 +30532,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>97</v>
@@ -30108,7 +30552,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>97</v>
@@ -30128,7 +30572,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>97</v>
@@ -30140,15 +30584,15 @@
         <v>59</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>97</v>
@@ -30177,16 +30621,16 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I158" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>100</v>
@@ -30206,13 +30650,13 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>97</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I159" s="2" t="s">
         <v>51</v>
@@ -30229,7 +30673,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>97</v>
@@ -30241,7 +30685,7 @@
         <v>109</v>
       </c>
       <c r="R160" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S160" s="3">
         <v>13635.280000000002</v>
@@ -30286,7 +30730,7 @@
         <v>2.0</v>
       </c>
       <c r="AM160" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="AN160" s="3">
         <v>2.0</v>
@@ -30318,7 +30762,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>103</v>
@@ -30338,13 +30782,13 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>51</v>
@@ -30358,7 +30802,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>103</v>
@@ -30378,7 +30822,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>103</v>
@@ -30411,7 +30855,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>103</v>
@@ -30444,7 +30888,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>103</v>
@@ -30477,7 +30921,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>103</v>
@@ -30570,7 +31014,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>108</v>
@@ -30590,7 +31034,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>108</v>
@@ -30610,13 +31054,13 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>55</v>
@@ -30630,7 +31074,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>108</v>
@@ -30659,7 +31103,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>108</v>
@@ -30682,7 +31126,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>108</v>
@@ -30691,7 +31135,7 @@
         <v>0.0</v>
       </c>
       <c r="Q173" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="R173" s="1" t="s">
         <v>54</v>
@@ -30745,7 +31189,7 @@
         <v>2.0</v>
       </c>
       <c r="AM173" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AN173" s="3">
         <v>1.0</v>
@@ -30777,7 +31221,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>49</v>
@@ -30797,7 +31241,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>49</v>
@@ -30817,13 +31261,13 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I176" s="2" t="s">
         <v>51</v>
@@ -30840,7 +31284,7 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>49</v>
@@ -30869,7 +31313,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>49</v>
@@ -30889,7 +31333,7 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>49</v>
@@ -30918,7 +31362,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>49</v>
@@ -30981,7 +31425,7 @@
         <v>1.0</v>
       </c>
       <c r="AM180" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AN180" s="3">
         <v>2.0</v>
@@ -31013,13 +31457,13 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>51</v>
@@ -31033,7 +31477,7 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>68</v>
@@ -31053,7 +31497,7 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>68</v>
@@ -31073,7 +31517,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>68</v>
@@ -31102,7 +31546,7 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>68</v>
@@ -31131,7 +31575,7 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>68</v>
@@ -31143,7 +31587,7 @@
         <v>69</v>
       </c>
       <c r="R186" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S186" s="3">
         <v>23310.47</v>
@@ -31191,7 +31635,7 @@
         <v>1.0</v>
       </c>
       <c r="AM186" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AN186" s="3">
         <v>2.0</v>
